--- a/data/dividends_info_20260522.xlsx
+++ b/data/dividends_info_20260522.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K162"/>
+  <dimension ref="A1:K172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>56.91999816894531</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1581166600407634</v>
+        <v>0.15535991632294</v>
       </c>
       <c r="J2" t="n">
         <v>297</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.34999847412109</v>
+        <v>55.20000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.264679348324255</v>
+        <v>1.26811592450189</v>
       </c>
       <c r="J3" t="n">
         <v>276</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J4" t="n">
         <v>206</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>56.93000030517578</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1580888802345881</v>
+        <v>0.15535991632294</v>
       </c>
       <c r="J6" t="n">
         <v>206</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.049999952316284</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I7" t="n">
-        <v>3.756097648343753</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J7" t="n">
         <v>185</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.51499938964844</v>
+        <v>23.29500007629395</v>
       </c>
       <c r="I8" t="n">
-        <v>1.148203304308215</v>
+        <v>1.159047001999216</v>
       </c>
       <c r="J8" t="n">
         <v>185</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.760000228881836</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I9" t="n">
-        <v>3.472222084248513</v>
+        <v>3.484320696428174</v>
       </c>
       <c r="J9" t="n">
         <v>178</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.28000020980835</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9469696593405037</v>
+        <v>0.9615384968074835</v>
       </c>
       <c r="J12" t="n">
         <v>136</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.96999979019165</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7676767972571169</v>
       </c>
       <c r="J13" t="n">
         <v>129</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.51499938964844</v>
+        <v>23.29500007629395</v>
       </c>
       <c r="I14" t="n">
-        <v>1.148203304308215</v>
+        <v>1.159047001999216</v>
       </c>
       <c r="J14" t="n">
         <v>122</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>56.93000030517578</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1580888802345881</v>
+        <v>0.15535991632294</v>
       </c>
       <c r="J15" t="n">
         <v>122</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.460000038146973</v>
+        <v>4.409999847412109</v>
       </c>
       <c r="I16" t="n">
-        <v>6.726457341570856</v>
+        <v>6.802721323812448</v>
       </c>
       <c r="J16" t="n">
         <v>115</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.96999979019165</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7676767972571169</v>
       </c>
       <c r="J18" t="n">
         <v>73</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.840000152587891</v>
+        <v>5.880000114440918</v>
       </c>
       <c r="I19" t="n">
-        <v>4.280821805958635</v>
+        <v>4.251700597522361</v>
       </c>
       <c r="J19" t="n">
         <v>66</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.729000091552734</v>
+        <v>9.697999954223633</v>
       </c>
       <c r="I20" t="n">
-        <v>2.672422628772988</v>
+        <v>2.680965160107738</v>
       </c>
       <c r="J20" t="n">
         <v>59</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>14.81999969482422</v>
+        <v>14.80000019073486</v>
       </c>
       <c r="I21" t="n">
-        <v>4.04858307932048</v>
+        <v>4.05405400180747</v>
       </c>
       <c r="J21" t="n">
         <v>59</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.624000072479248</v>
+        <v>3.598000049591064</v>
       </c>
       <c r="I22" t="n">
-        <v>6.0706400551889</v>
+        <v>6.114507975757377</v>
       </c>
       <c r="J22" t="n">
         <v>59</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.050000190734863</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="I24" t="n">
-        <v>1.652892509873682</v>
+        <v>1.655629149529345</v>
       </c>
       <c r="J24" t="n">
         <v>59</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>17.85000038146973</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
-        <v>2.106442532014339</v>
+        <v>2.088888888888889</v>
       </c>
       <c r="J25" t="n">
         <v>59</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.164999961853027</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="I26" t="n">
-        <v>2.881152487372688</v>
+        <v>2.816901257103866</v>
       </c>
       <c r="J26" t="n">
         <v>52</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.660000085830688</v>
+        <v>2.640000104904175</v>
       </c>
       <c r="I28" t="n">
-        <v>5.639097562403148</v>
+        <v>5.681817956043021</v>
       </c>
       <c r="J28" t="n">
         <v>52</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.140000104904175</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I29" t="n">
-        <v>3.971962422114281</v>
+        <v>3.935185028814982</v>
       </c>
       <c r="J29" t="n">
         <v>45</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.380000114440918</v>
+        <v>4.539999961853027</v>
       </c>
       <c r="I30" t="n">
-        <v>1.598173474224557</v>
+        <v>1.541850233219586</v>
       </c>
       <c r="J30" t="n">
         <v>45</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>30.95000076293945</v>
+        <v>31.39999961853027</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4846526536426291</v>
+        <v>0.4777070121729542</v>
       </c>
       <c r="J31" t="n">
         <v>45</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.800000190734863</v>
+        <v>5.75</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6896551497342619</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="J32" t="n">
         <v>38</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23.26000022888184</v>
+        <v>23.07999992370605</v>
       </c>
       <c r="I33" t="n">
-        <v>4.084264792140411</v>
+        <v>4.11611786455957</v>
       </c>
       <c r="J33" t="n">
         <v>31</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>30.85000038146973</v>
+        <v>31.14999961853027</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6320907539344089</v>
+        <v>0.6260032179390458</v>
       </c>
       <c r="J34" t="n">
         <v>31</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.195000171661377</v>
+        <v>5.230000019073486</v>
       </c>
       <c r="I36" t="n">
-        <v>5.582290479641257</v>
+        <v>5.544933058171853</v>
       </c>
       <c r="J36" t="n">
         <v>31</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.891999959945679</v>
+        <v>3.910000085830688</v>
       </c>
       <c r="I37" t="n">
-        <v>4.110996959060429</v>
+        <v>4.09207152142575</v>
       </c>
       <c r="J37" t="n">
         <v>31</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>51.08000183105469</v>
+        <v>52.31999969482422</v>
       </c>
       <c r="I39" t="n">
-        <v>1.233359391966553</v>
+        <v>1.204128447390498</v>
       </c>
       <c r="J39" t="n">
         <v>31</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.54999923706055</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="I41" t="n">
-        <v>3.989769976672784</v>
+        <v>4.06249983857076</v>
       </c>
       <c r="J41" t="n">
         <v>31</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>24.94000053405762</v>
+        <v>25.02000045776367</v>
       </c>
       <c r="I42" t="n">
-        <v>3.408179558132949</v>
+        <v>3.397282112104223</v>
       </c>
       <c r="J42" t="n">
         <v>31</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>56.93000030517578</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1580888802345881</v>
+        <v>0.15535991632294</v>
       </c>
       <c r="J43" t="n">
         <v>31</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.330000042915344</v>
+        <v>1.389999985694885</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7518796749870864</v>
+        <v>0.7194244678355752</v>
       </c>
       <c r="J44" t="n">
         <v>31</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.392000198364258</v>
+        <v>6.386000156402588</v>
       </c>
       <c r="I45" t="n">
-        <v>2.836357859413013</v>
+        <v>2.839022792979876</v>
       </c>
       <c r="J45" t="n">
         <v>31</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.609999656677246</v>
+        <v>8.640000343322754</v>
       </c>
       <c r="I46" t="n">
-        <v>3.019744603571084</v>
+        <v>3.009259139682045</v>
       </c>
       <c r="J46" t="n">
         <v>31</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>10.05500030517578</v>
+        <v>9.949999809265137</v>
       </c>
       <c r="I47" t="n">
-        <v>2.754848250550675</v>
+        <v>2.783919651355833</v>
       </c>
       <c r="J47" t="n">
         <v>31</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.149999976158142</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="I48" t="n">
-        <v>1.173913067815886</v>
+        <v>1.15384619616898</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.032000064849854</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="I49" t="n">
-        <v>3.627968260134166</v>
+        <v>3.63036307058268</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.244999885559082</v>
+        <v>3.285000085830688</v>
       </c>
       <c r="I51" t="n">
-        <v>4.93066273167013</v>
+        <v>4.87062392144627</v>
       </c>
       <c r="J51" t="n">
         <v>17</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28.54999923706055</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="I53" t="n">
-        <v>3.887916040849196</v>
+        <v>3.901581617691721</v>
       </c>
       <c r="J53" t="n">
         <v>13</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8859999775886536</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="I54" t="n">
-        <v>3.386004600321582</v>
+        <v>3.448275843169356</v>
       </c>
       <c r="J54" t="n">
         <v>10</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.5139999985694885</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I55" t="n">
-        <v>4.47470818365977</v>
+        <v>4.509804005899691</v>
       </c>
       <c r="J55" t="n">
         <v>10</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>19.64999961853027</v>
+        <v>20</v>
       </c>
       <c r="I56" t="n">
-        <v>3.053435173780819</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>10</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8.880000114440918</v>
+        <v>9</v>
       </c>
       <c r="I57" t="n">
-        <v>2.252252223226372</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="J57" t="n">
         <v>10</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.535000085830688</v>
+        <v>2.555000066757202</v>
       </c>
       <c r="I58" t="n">
-        <v>7.100591475562661</v>
+        <v>7.045009600663354</v>
       </c>
       <c r="J58" t="n">
         <v>3</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>8.25</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I59" t="n">
-        <v>3.636363636363636</v>
+        <v>3.614457748264686</v>
       </c>
       <c r="J59" t="n">
         <v>3</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14.94999980926514</v>
+        <v>15.09000015258789</v>
       </c>
       <c r="I60" t="n">
-        <v>1.672240824010343</v>
+        <v>1.656726292061208</v>
       </c>
       <c r="J60" t="n">
         <v>3</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.430000066757202</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8746355514903141</v>
+        <v>0.8720930087495459</v>
       </c>
       <c r="J61" t="n">
         <v>3</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.179999828338623</v>
+        <v>4.150000095367432</v>
       </c>
       <c r="I62" t="n">
-        <v>3.588516893782237</v>
+        <v>3.614457748264686</v>
       </c>
       <c r="J62" t="n">
         <v>3</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.282999992370605</v>
+        <v>2.275000095367432</v>
       </c>
       <c r="I64" t="n">
-        <v>4.555409564062645</v>
+        <v>4.571428379795436</v>
       </c>
       <c r="J64" t="n">
         <v>-4</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.54500007629395</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I65" t="n">
-        <v>2.750118519694889</v>
+        <v>2.801932263879001</v>
       </c>
       <c r="J65" t="n">
         <v>-4</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.049999952316284</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I66" t="n">
-        <v>3.756097648343753</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J66" t="n">
         <v>-4</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>38.68000030517578</v>
+        <v>38.93999862670898</v>
       </c>
       <c r="I67" t="n">
-        <v>4.239917236455014</v>
+        <v>4.211607749968235</v>
       </c>
       <c r="J67" t="n">
         <v>-4</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>34.77999877929688</v>
+        <v>34.72000122070312</v>
       </c>
       <c r="I68" t="n">
-        <v>5.750431484173942</v>
+        <v>5.760368461068555</v>
       </c>
       <c r="J68" t="n">
         <v>-4</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3.165999889373779</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="I69" t="n">
-        <v>3.158559807144515</v>
+        <v>3.124999953433872</v>
       </c>
       <c r="J69" t="n">
         <v>-4</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>35.27000045776367</v>
+        <v>36.09000015258789</v>
       </c>
       <c r="I70" t="n">
-        <v>0.420924292807376</v>
+        <v>0.4113604859304897</v>
       </c>
       <c r="J70" t="n">
         <v>-4</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19.40999984741211</v>
+        <v>19.38999938964844</v>
       </c>
       <c r="I71" t="n">
-        <v>4.739824869821736</v>
+        <v>4.744713919336955</v>
       </c>
       <c r="J71" t="n">
         <v>-4</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>10.88000011444092</v>
+        <v>10.85999965667725</v>
       </c>
       <c r="I72" t="n">
-        <v>2.757352912173346</v>
+        <v>2.762431026556669</v>
       </c>
       <c r="J72" t="n">
         <v>-4</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>83.41999816894531</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="I73" t="n">
-        <v>1.246703455799355</v>
+        <v>1.263669454964603</v>
       </c>
       <c r="J73" t="n">
         <v>-4</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>43.88000106811523</v>
+        <v>43.7400016784668</v>
       </c>
       <c r="I74" t="n">
-        <v>1.595259760621667</v>
+        <v>1.600365736484665</v>
       </c>
       <c r="J74" t="n">
         <v>-4</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>55.34999847412109</v>
+        <v>55.20000076293945</v>
       </c>
       <c r="I75" t="n">
-        <v>3.974706523304803</v>
+        <v>3.985507191291655</v>
       </c>
       <c r="J75" t="n">
         <v>-4</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8.640000343322754</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="I76" t="n">
-        <v>9.953703308179069</v>
+        <v>9.873708337927429</v>
       </c>
       <c r="J76" t="n">
         <v>-4</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.48600006103516</v>
+        <v>11.49199962615967</v>
       </c>
       <c r="I77" t="n">
-        <v>4.875500583529782</v>
+        <v>4.872955257719041</v>
       </c>
       <c r="J77" t="n">
         <v>-4</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8.710000038146973</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I79" t="n">
-        <v>3.444316862067708</v>
+        <v>3.409090835200855</v>
       </c>
       <c r="J79" t="n">
         <v>-4</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2.200000047683716</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I80" t="n">
-        <v>4.909090802689231</v>
+        <v>4.954128288658833</v>
       </c>
       <c r="J80" t="n">
         <v>-4</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>87.69999694824219</v>
+        <v>89</v>
       </c>
       <c r="I81" t="n">
-        <v>2.348916843424462</v>
+        <v>2.314606741573034</v>
       </c>
       <c r="J81" t="n">
         <v>-4</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>13.39000034332275</v>
+        <v>13.63000011444092</v>
       </c>
       <c r="I83" t="n">
-        <v>2.240477911186927</v>
+        <v>2.201027127521088</v>
       </c>
       <c r="J83" t="n">
         <v>-4</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>51.59999847412109</v>
+        <v>50.79999923706055</v>
       </c>
       <c r="I84" t="n">
-        <v>1.647286870417835</v>
+        <v>1.673228371586062</v>
       </c>
       <c r="J84" t="n">
         <v>-4</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>34.38000106811523</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="I85" t="n">
-        <v>2.4723675788024</v>
+        <v>2.421652526927308</v>
       </c>
       <c r="J85" t="n">
         <v>-4</v>
@@ -4439,11 +4439,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.093</v>
+        <v>1.3</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4467,14 +4467,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IT0005345233</t>
+          <t>IT0003492391</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>5.179999828338623</v>
+        <v>64.59999847412109</v>
       </c>
       <c r="I86" t="n">
-        <v>1.795366854863928</v>
+        <v>2.01238394846214</v>
       </c>
       <c r="J86" t="n">
         <v>-4</v>
@@ -4486,11 +4486,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4509,19 +4509,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IT0005359101</t>
+          <t>IT0001463063</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>6.900000095367432</v>
+        <v>6.960000038146973</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8695652053727246</v>
+        <v>8.620689607923389</v>
       </c>
       <c r="J87" t="n">
         <v>-4</v>
@@ -4533,11 +4533,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4561,14 +4561,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IT0001078911</t>
+          <t>IT0005669558</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>35.02000045776367</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I88" t="n">
-        <v>0.999428884708674</v>
+        <v>7.704918153245615</v>
       </c>
       <c r="J88" t="n">
         <v>-4</v>
@@ -4580,11 +4580,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5543</v>
+        <v>0.2</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4603,19 +4603,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IT0005090300</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6.940000057220459</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I89" t="n">
-        <v>7.987031634434925</v>
+        <v>3.484320696428174</v>
       </c>
       <c r="J89" t="n">
         <v>-4</v>
@@ -4627,11 +4627,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4655,14 +4655,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IT0001077780</t>
+          <t>IT0001157020</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>2.240000009536743</v>
+        <v>22.94000053405762</v>
       </c>
       <c r="I90" t="n">
-        <v>2.678571417167479</v>
+        <v>4.35919780610014</v>
       </c>
       <c r="J90" t="n">
         <v>-4</v>
@@ -4674,11 +4674,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.2</v>
+        <v>0.215</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>IT0003411417</t>
+          <t>IT0004356751</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>12.89999961853027</v>
+        <v>4.710000038146973</v>
       </c>
       <c r="I91" t="n">
-        <v>1.550387642746198</v>
+        <v>4.56475580167057</v>
       </c>
       <c r="J91" t="n">
         <v>-4</v>
@@ -4721,11 +4721,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.103</v>
+        <v>0.27</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4744,19 +4744,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IT0005186371</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>7.090000152587891</v>
+        <v>23.29500007629395</v>
       </c>
       <c r="I92" t="n">
-        <v>1.452750321343849</v>
+        <v>1.159047001999216</v>
       </c>
       <c r="J92" t="n">
         <v>-4</v>
@@ -4768,11 +4768,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4796,14 +4796,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0005521247</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>5.64300012588501</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I93" t="n">
-        <v>3.367003291891681</v>
+        <v>2.150537590302958</v>
       </c>
       <c r="J93" t="n">
         <v>-4</v>
@@ -4815,11 +4815,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.432</v>
+        <v>0.24</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>10.17500019073486</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="I94" t="n">
-        <v>4.245700166112723</v>
+        <v>2.752293493699352</v>
       </c>
       <c r="J94" t="n">
         <v>-4</v>
@@ -4862,11 +4862,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>24.90999984741211</v>
+        <v>20.96999931335449</v>
       </c>
       <c r="I95" t="n">
-        <v>1.766358902831191</v>
+        <v>3.76728672326135</v>
       </c>
       <c r="J95" t="n">
         <v>-4</v>
@@ -4909,11 +4909,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.03</v>
+        <v>0.093</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IT0004522162</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.019999980926514</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="I96" t="n">
-        <v>2.941176525586755</v>
+        <v>1.728624498545469</v>
       </c>
       <c r="J96" t="n">
         <v>-4</v>
@@ -4956,11 +4956,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.47</v>
+        <v>0.06</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4979,19 +4979,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.5</v>
+        <v>6.900000095367432</v>
       </c>
       <c r="I97" t="n">
-        <v>6.266666666666667</v>
+        <v>0.8695652053727246</v>
       </c>
       <c r="J97" t="n">
         <v>-4</v>
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>51.54000091552734</v>
+        <v>34.86000061035156</v>
       </c>
       <c r="I98" t="n">
-        <v>2.716336777514928</v>
+        <v>1.004016046678062</v>
       </c>
       <c r="J98" t="n">
         <v>-4</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.3</v>
+        <v>0.5543</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0005090300</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3.394000053405762</v>
+        <v>6.835000038146973</v>
       </c>
       <c r="I99" t="n">
-        <v>8.839127733629832</v>
+        <v>8.109729289047312</v>
       </c>
       <c r="J99" t="n">
         <v>-4</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>13.75</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8727272727272728</v>
+        <v>2.678571417167479</v>
       </c>
       <c r="J100" t="n">
         <v>-4</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3.440000057220459</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I101" t="n">
-        <v>4.941860382914093</v>
+        <v>1.562499976716936</v>
       </c>
       <c r="J101" t="n">
         <v>-4</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7</v>
+        <v>0.103</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>22.79999923706055</v>
+        <v>7.054999828338623</v>
       </c>
       <c r="I102" t="n">
-        <v>3.070175541331493</v>
+        <v>1.459957512490194</v>
       </c>
       <c r="J102" t="n">
         <v>-4</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.035</v>
+        <v>0.19</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2.359999895095825</v>
+        <v>5.618000030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>1.483050913380607</v>
+        <v>3.381986453682799</v>
       </c>
       <c r="J103" t="n">
         <v>-4</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.33</v>
+        <v>0.432</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.639999866485596</v>
+        <v>10.13500022888184</v>
       </c>
       <c r="I104" t="n">
-        <v>5.851063968298106</v>
+        <v>4.262456736497393</v>
       </c>
       <c r="J104" t="n">
         <v>-4</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.8939999938011169</v>
+        <v>25.11000061035156</v>
       </c>
       <c r="I105" t="n">
-        <v>7.829977682927423</v>
+        <v>1.75228988173983</v>
       </c>
       <c r="J105" t="n">
         <v>-4</v>
@@ -5379,11 +5379,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.71</v>
+        <v>0.03</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0004522162</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>51.54999923706055</v>
+        <v>1.019999980926514</v>
       </c>
       <c r="I106" t="n">
-        <v>1.377303609132866</v>
+        <v>2.941176525586755</v>
       </c>
       <c r="J106" t="n">
         <v>-4</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.35</v>
+        <v>0.47</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>103.4000015258789</v>
+        <v>7.369999885559082</v>
       </c>
       <c r="I107" t="n">
-        <v>1.305609265065748</v>
+        <v>6.377204983692428</v>
       </c>
       <c r="J107" t="n">
         <v>-4</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0005543613</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.159999847412109</v>
+        <v>51.52000045776367</v>
       </c>
       <c r="I108" t="n">
-        <v>1.11731845956554</v>
+        <v>2.717391280203358</v>
       </c>
       <c r="J108" t="n">
         <v>-4</v>
@@ -5520,11 +5520,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0001017851</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>260</v>
+        <v>3.381999969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>1.153846153846154</v>
+        <v>8.870490913869277</v>
       </c>
       <c r="J109" t="n">
         <v>-4</v>
@@ -5567,11 +5567,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>4.251999855041504</v>
+        <v>14.25</v>
       </c>
       <c r="I110" t="n">
-        <v>3.99811866875853</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="J110" t="n">
         <v>-4</v>
@@ -5614,11 +5614,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.297</v>
+        <v>0.17</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5642,14 +5642,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005568461</t>
+          <t>IT0005453748</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>7.300000190734863</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="I111" t="n">
-        <v>4.068493044383087</v>
+        <v>5.029585628523551</v>
       </c>
       <c r="J111" t="n">
         <v>-4</v>
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0001206769</t>
+          <t>IT0005373789</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>56.90000152587891</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7908611387212947</v>
+        <v>3.083700336886491</v>
       </c>
       <c r="J112" t="n">
         <v>-4</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0005595423</t>
+          <t>IT0005378143</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>5.400000095367432</v>
+        <v>2.480000019073486</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7407407276587887</v>
+        <v>1.411290311726522</v>
       </c>
       <c r="J113" t="n">
         <v>-4</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1.05</v>
+        <v>0.33</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0003549422</t>
+          <t>IT0005054967</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>36.45999908447266</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="I114" t="n">
-        <v>2.879868421190299</v>
+        <v>5.871886240566558</v>
       </c>
       <c r="J114" t="n">
         <v>-4</v>
@@ -5802,11 +5802,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0005621070</t>
+          <t>IT0004931496</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1.450000047683716</v>
+        <v>0.8859999775886536</v>
       </c>
       <c r="I115" t="n">
-        <v>3.44827574867131</v>
+        <v>7.90067740075036</v>
       </c>
       <c r="J115" t="n">
         <v>-4</v>
@@ -5849,11 +5849,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0005162406</t>
+          <t>IT0003828271</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>20.34000015258789</v>
+        <v>51.29999923706055</v>
       </c>
       <c r="I116" t="n">
-        <v>1.868239907321987</v>
+        <v>1.384015615125148</v>
       </c>
       <c r="J116" t="n">
         <v>-4</v>
@@ -5896,15 +5896,15 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6</v>
+        <v>1.35</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5924,14 +5924,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>26.48999977111816</v>
+        <v>104.9000015258789</v>
       </c>
       <c r="I117" t="n">
-        <v>2.26500568208451</v>
+        <v>1.286939924082798</v>
       </c>
       <c r="J117" t="n">
         <v>-4</v>
@@ -5943,11 +5943,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>IT0001454435</t>
+          <t>IT0005543613</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>35.65000152587891</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9817671389044105</v>
+        <v>1.111111140545505</v>
       </c>
       <c r="J118" t="n">
         <v>-4</v>
@@ -5990,11 +5990,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.017</v>
+        <v>3</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6018,14 +6018,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0005658841</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3.299999952316284</v>
+        <v>260</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5151515225952542</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="J119" t="n">
         <v>-4</v>
@@ -6037,11 +6037,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0005573065</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>2.714999914169312</v>
+        <v>4.230000019073486</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3683241368742226</v>
+        <v>4.018912511429155</v>
       </c>
       <c r="J120" t="n">
         <v>-4</v>
@@ -6084,11 +6084,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.12</v>
+        <v>0.297</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6112,14 +6112,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>21.6299991607666</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I121" t="n">
-        <v>5.177993728411709</v>
+        <v>4.068493044383087</v>
       </c>
       <c r="J121" t="n">
         <v>-4</v>
@@ -6131,11 +6131,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6159,14 +6159,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1.480000019073486</v>
+        <v>57</v>
       </c>
       <c r="I122" t="n">
-        <v>6.756756669679118</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="J122" t="n">
         <v>-4</v>
@@ -6178,11 +6178,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6206,14 +6206,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>9.140000343322754</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="I123" t="n">
-        <v>2.844638842819558</v>
+        <v>0.7490636490078573</v>
       </c>
       <c r="J123" t="n">
         <v>-4</v>
@@ -6225,11 +6225,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6253,14 +6253,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.194000005722046</v>
+        <v>36.7599983215332</v>
       </c>
       <c r="I124" t="n">
-        <v>4.20692797444292</v>
+        <v>2.856365745220758</v>
       </c>
       <c r="J124" t="n">
         <v>-4</v>
@@ -6272,11 +6272,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6300,30 +6300,30 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>8.960000038146973</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I125" t="n">
-        <v>3.906249983369239</v>
+        <v>3.44827574867131</v>
       </c>
       <c r="J125" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K125" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.096</v>
+        <v>0.38</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6347,44 +6347,44 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>5.300000190734863</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="I126" t="n">
-        <v>1.811320689531697</v>
+        <v>1.890547227801665</v>
       </c>
       <c r="J126" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K126" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6394,30 +6394,30 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IT0005416281</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>6.150000095367432</v>
+        <v>26.44000053405762</v>
       </c>
       <c r="I127" t="n">
-        <v>4.878048704844394</v>
+        <v>2.269288910290052</v>
       </c>
       <c r="J127" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K127" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6441,30 +6441,30 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT0005037905</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>11.80000019073486</v>
+        <v>35.45000076293945</v>
       </c>
       <c r="I128" t="n">
-        <v>1.694915226840727</v>
+        <v>0.9873060436317422</v>
       </c>
       <c r="J128" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K128" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.06</v>
+        <v>0.017</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6473,45 +6473,45 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9</v>
+        <v>3.259999990463257</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5214723941635424</v>
       </c>
       <c r="J129" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K129" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6535,30 +6535,30 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0005075764</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>18.89999961853027</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I130" t="n">
-        <v>2.64550269889837</v>
+        <v>0.3703703638293944</v>
       </c>
       <c r="J130" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K130" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.06</v>
+        <v>1.12</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6567,12 +6567,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6582,30 +6582,30 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0004376858</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.240000009536743</v>
+        <v>21.60000038146973</v>
       </c>
       <c r="I131" t="n">
-        <v>2.678571417167479</v>
+        <v>5.185185093611522</v>
       </c>
       <c r="J131" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K131" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6629,30 +6629,30 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.30000019073486</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I132" t="n">
-        <v>3.267973815469507</v>
+        <v>6.896551497342619</v>
       </c>
       <c r="J132" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K132" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6676,30 +6676,30 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0005430951</t>
+          <t>IT0003865588</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>3.660000085830688</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I133" t="n">
-        <v>2.73224037308468</v>
+        <v>2.921348439820898</v>
       </c>
       <c r="J133" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K133" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.11</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6708,12 +6708,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6723,30 +6723,30 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>3.029999971389771</v>
+        <v>2.164000034332275</v>
       </c>
       <c r="I134" t="n">
-        <v>3.63036307058268</v>
+        <v>4.26524947022379</v>
       </c>
       <c r="J134" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="K134" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6770,14 +6770,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>9.149999618530273</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I135" t="n">
-        <v>0.9289617873629289</v>
+        <v>3.846153684924045</v>
       </c>
       <c r="J135" t="n">
         <v>-11</v>
@@ -6789,11 +6789,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.095</v>
+        <v>0.096</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0005543332</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>4.739999771118164</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="I136" t="n">
-        <v>2.004219506061063</v>
+        <v>1.811320689531697</v>
       </c>
       <c r="J136" t="n">
         <v>-11</v>
@@ -6836,11 +6836,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0005521551</t>
+          <t>IT0005416281</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1.279999971389771</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I137" t="n">
-        <v>2.343750052386896</v>
+        <v>4.838709826275912</v>
       </c>
       <c r="J137" t="n">
         <v>-11</v>
@@ -6883,11 +6883,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0005246142</t>
+          <t>IT0005037905</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>8.149999618530273</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I138" t="n">
-        <v>1.104294530215329</v>
+        <v>1.694915226840727</v>
       </c>
       <c r="J138" t="n">
         <v>-11</v>
@@ -6930,11 +6930,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6953,19 +6953,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0005532525</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>8.399999618530273</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I139" t="n">
-        <v>1.190476244539363</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J139" t="n">
         <v>-11</v>
@@ -6977,11 +6977,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7005,14 +7005,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>7.139999866485596</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I140" t="n">
-        <v>3.081232550614696</v>
+        <v>2.64550269889837</v>
       </c>
       <c r="J140" t="n">
         <v>-11</v>
@@ -7024,11 +7024,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.61</v>
+        <v>0.06</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7037,12 +7037,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7052,30 +7052,30 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0004376858</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>25.25</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I141" t="n">
-        <v>2.415841584158416</v>
+        <v>2.678571417167479</v>
       </c>
       <c r="J141" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K141" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7099,30 +7099,30 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>2.869999885559082</v>
+        <v>15.15999984741211</v>
       </c>
       <c r="I142" t="n">
-        <v>5.226481044642261</v>
+        <v>3.298153067497244</v>
       </c>
       <c r="J142" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K142" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7146,30 +7146,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005430951</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>11.60000038146973</v>
+        <v>3.680000066757202</v>
       </c>
       <c r="I143" t="n">
-        <v>6.034482560174792</v>
+        <v>2.71739125505287</v>
       </c>
       <c r="J143" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K143" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5105</v>
+        <v>0.11</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7193,44 +7193,44 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>8.810000419616699</v>
+        <v>3.049999952316284</v>
       </c>
       <c r="I144" t="n">
-        <v>5.794551369864867</v>
+        <v>3.606557433434118</v>
       </c>
       <c r="J144" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K144" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.27</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7240,30 +7240,30 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0005545238</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>8.239999771118164</v>
+        <v>9.149999618530273</v>
       </c>
       <c r="I145" t="n">
-        <v>3.276699120142829</v>
+        <v>0.9289617873629289</v>
       </c>
       <c r="J145" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K145" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.35</v>
+        <v>0.095</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7272,12 +7272,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7287,30 +7287,30 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0005466963</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>6.605000019073486</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="I146" t="n">
-        <v>5.29901588174554</v>
+        <v>1.975051998547481</v>
       </c>
       <c r="J146" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K146" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1.1</v>
+        <v>0.03</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7334,30 +7334,30 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0005521551</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>42</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="I147" t="n">
-        <v>2.619047619047619</v>
+        <v>2.362204759886205</v>
       </c>
       <c r="J147" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K147" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.75</v>
+        <v>0.09</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7366,45 +7366,45 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0005246142</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>17.20000076293945</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="I148" t="n">
-        <v>4.360464922862167</v>
+        <v>1.104294530215329</v>
       </c>
       <c r="J148" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K148" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7428,30 +7428,30 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0005532525</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>10.44999980926514</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I149" t="n">
-        <v>4.114832610989668</v>
+        <v>1.190476244539363</v>
       </c>
       <c r="J149" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K149" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7475,30 +7475,30 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>4.360000133514404</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I150" t="n">
-        <v>3.440366867124189</v>
+        <v>3.055555636500137</v>
       </c>
       <c r="J150" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K150" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.197169</v>
+        <v>0.61</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7522,14 +7522,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>11.85999965667725</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="I151" t="n">
-        <v>1.662470537163909</v>
+        <v>2.420634847349292</v>
       </c>
       <c r="J151" t="n">
         <v>-18</v>
@@ -7541,11 +7541,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1.1</v>
+        <v>0.15</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>29.45000076293945</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="I152" t="n">
-        <v>3.735144215630259</v>
+        <v>5.226481044642261</v>
       </c>
       <c r="J152" t="n">
         <v>-18</v>
@@ -7588,11 +7588,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7616,14 +7616,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>65.69999694824219</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7153729403827238</v>
+        <v>6.140351082662987</v>
       </c>
       <c r="J153" t="n">
         <v>-18</v>
@@ -7635,11 +7635,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.2</v>
+        <v>0.5105</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7663,14 +7663,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>85.40000152587891</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="I154" t="n">
-        <v>1.405152199717891</v>
+        <v>5.647123917635031</v>
       </c>
       <c r="J154" t="n">
         <v>-18</v>
@@ -7682,7 +7682,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7710,14 +7710,14 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>22.29999923706055</v>
+        <v>8.175000190734863</v>
       </c>
       <c r="I155" t="n">
-        <v>1.210762373261811</v>
+        <v>3.302752216519879</v>
       </c>
       <c r="J155" t="n">
         <v>-18</v>
@@ -7729,11 +7729,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -7757,14 +7757,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>10.19999980926514</v>
+        <v>6.675000190734863</v>
       </c>
       <c r="I156" t="n">
-        <v>3.725490265743223</v>
+        <v>5.243445543055</v>
       </c>
       <c r="J156" t="n">
         <v>-18</v>
@@ -7776,11 +7776,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7804,14 +7804,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>33.09999847412109</v>
+        <v>42</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9063444526577609</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="J157" t="n">
         <v>-18</v>
@@ -7823,11 +7823,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.007</v>
+        <v>0.75</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -7836,45 +7836,45 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IT0001073045</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0.1713999956846237</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="I158" t="n">
-        <v>4.084014105157863</v>
+        <v>4.385964814437848</v>
       </c>
       <c r="J158" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K158" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.16</v>
+        <v>0.43</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -7883,12 +7883,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7898,30 +7898,30 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>IT0001033700</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>6.739999771118164</v>
+        <v>10.80000019073486</v>
       </c>
       <c r="I159" t="n">
-        <v>2.37388732097028</v>
+        <v>3.981481411165989</v>
       </c>
       <c r="J159" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K159" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.065</v>
+        <v>0.15</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7945,30 +7945,30 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>IT0003372205</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>2.065000057220459</v>
+        <v>4.400000095367432</v>
       </c>
       <c r="I160" t="n">
-        <v>3.147699670647545</v>
+        <v>3.409090835200855</v>
       </c>
       <c r="J160" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K160" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.25</v>
+        <v>0.197169</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7977,12 +7977,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7992,66 +7992,536 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>IT0003365613</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>8.119999885559082</v>
+        <v>11.96000003814697</v>
       </c>
       <c r="I161" t="n">
-        <v>3.07881777738211</v>
+        <v>1.648570228855522</v>
       </c>
       <c r="J161" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K161" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>ITALMOBILIARE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>IT0005253205</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>29</v>
+      </c>
+      <c r="I162" t="n">
+        <v>3.793103448275863</v>
+      </c>
+      <c r="J162" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K162" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>LU-VE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>IT0005107492</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>66.09999847412109</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.7110438893338407</v>
+      </c>
+      <c r="J163" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Pharmanutra S.p.A.</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>IT0005274094</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>85.30000305175781</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1.406799480736092</v>
+      </c>
+      <c r="J164" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>REVO Insurance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>IT0005513202</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>22.10000038146973</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1.221719435925386</v>
+      </c>
+      <c r="J165" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>VALSOIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>IT0001018362</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>10.19999980926514</v>
+      </c>
+      <c r="I166" t="n">
+        <v>3.725490265743223</v>
+      </c>
+      <c r="J166" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>WIIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>IT0005440893</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>33.70000076293945</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.8902076949799829</v>
+      </c>
+      <c r="J167" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Banca Profilo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>IT0001073045</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>0.1721999943256378</v>
+      </c>
+      <c r="I168" t="n">
+        <v>4.065040784358384</v>
+      </c>
+      <c r="J168" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K168" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Basic Net S.p.A.</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>IT0001033700</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>6.710000038146973</v>
+      </c>
+      <c r="I169" t="n">
+        <v>2.384500731600375</v>
+      </c>
+      <c r="J169" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>EDISON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>IT0003372205</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>2.059999942779541</v>
+      </c>
+      <c r="I170" t="n">
+        <v>3.155339893470873</v>
+      </c>
+      <c r="J170" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Fiera Milano S.p.A</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>IT0003365613</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>8.220000267028809</v>
+      </c>
+      <c r="I171" t="n">
+        <v>3.041362431614187</v>
+      </c>
+      <c r="J171" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K171" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
           <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
-      <c r="B162" t="n">
+      <c r="B172" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
         <is>
           <t>IT0005549255</t>
         </is>
       </c>
-      <c r="H162" t="n">
+      <c r="H172" t="n">
         <v>1.340000033378601</v>
       </c>
-      <c r="I162" t="n">
+      <c r="I172" t="n">
         <v>5.223880466891178</v>
       </c>
-      <c r="J162" t="n">
+      <c r="J172" t="n">
         <v>-25</v>
       </c>
-      <c r="K162" t="n">
+      <c r="K172" t="n">
         <v>-23</v>
       </c>
     </row>
@@ -9793,61 +10263,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BUZZI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>